--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-05-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-05-2025.xlsx
@@ -134,6 +134,191 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Price Tracker</author>
+  </authors>
+  <commentList>
+    <comment ref="F2" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £12.36</t>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £14.50</t>
+      </text>
+    </comment>
+    <comment ref="F4" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £17.15</t>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £18.22</t>
+      </text>
+    </comment>
+    <comment ref="F6" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £23.11</t>
+      </text>
+    </comment>
+    <comment ref="F7" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £25.75</t>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £25.26</t>
+      </text>
+    </comment>
+    <comment ref="L8" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £24.08</t>
+      </text>
+    </comment>
+    <comment ref="F9" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £28.97</t>
+      </text>
+    </comment>
+    <comment ref="F10" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £31.95</t>
+      </text>
+    </comment>
+    <comment ref="F11" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £31.12</t>
+      </text>
+    </comment>
+    <comment ref="L11" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £30.00</t>
+      </text>
+    </comment>
+    <comment ref="F12" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £40.80</t>
+      </text>
+    </comment>
+    <comment ref="F13" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £38.50</t>
+      </text>
+    </comment>
+    <comment ref="F14" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £45.69</t>
+      </text>
+    </comment>
+    <comment ref="F15" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £46.95</t>
+      </text>
+    </comment>
+    <comment ref="F16" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £48.32</t>
+      </text>
+    </comment>
+    <comment ref="F17" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £784.70</t>
+      </text>
+    </comment>
+    <comment ref="L17" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £785.93</t>
+      </text>
+    </comment>
+    <comment ref="F18" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £1,005.07</t>
+      </text>
+    </comment>
+    <comment ref="F19" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £38.16</t>
+      </text>
+    </comment>
+    <comment ref="L19" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £31.88</t>
+      </text>
+    </comment>
+    <comment ref="F20" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £47.84</t>
+      </text>
+    </comment>
+    <comment ref="L20" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £38.70</t>
+      </text>
+    </comment>
+    <comment ref="F21" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £50.47</t>
+      </text>
+    </comment>
+    <comment ref="L21" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £40.25</t>
+      </text>
+    </comment>
+    <comment ref="F22" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £56.44</t>
+      </text>
+    </comment>
+    <comment ref="L22" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £46.95</t>
+      </text>
+    </comment>
+    <comment ref="F23" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £48.91</t>
+      </text>
+    </comment>
+    <comment ref="F24" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £47.25</t>
+      </text>
+    </comment>
+    <comment ref="F26" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £48.32</t>
+      </text>
+    </comment>
+    <comment ref="L26" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £47.08</t>
+      </text>
+    </comment>
+    <comment ref="F27" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £1,252.32</t>
+      </text>
+    </comment>
+    <comment ref="F28" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £1,370.57</t>
+      </text>
+    </comment>
+    <comment ref="F29" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £1,306.07</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3243,5 +3428,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-05-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-05-2025.xlsx
@@ -134,191 +134,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Price Tracker</author>
-  </authors>
-  <commentList>
-    <comment ref="F2" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £12.36</t>
-      </text>
-    </comment>
-    <comment ref="F3" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £14.50</t>
-      </text>
-    </comment>
-    <comment ref="F4" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £17.15</t>
-      </text>
-    </comment>
-    <comment ref="F5" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £18.22</t>
-      </text>
-    </comment>
-    <comment ref="F6" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £23.11</t>
-      </text>
-    </comment>
-    <comment ref="F7" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £25.75</t>
-      </text>
-    </comment>
-    <comment ref="F8" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £25.26</t>
-      </text>
-    </comment>
-    <comment ref="L8" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £24.08</t>
-      </text>
-    </comment>
-    <comment ref="F9" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £28.97</t>
-      </text>
-    </comment>
-    <comment ref="F10" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £31.95</t>
-      </text>
-    </comment>
-    <comment ref="F11" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £31.12</t>
-      </text>
-    </comment>
-    <comment ref="L11" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £30.00</t>
-      </text>
-    </comment>
-    <comment ref="F12" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £40.80</t>
-      </text>
-    </comment>
-    <comment ref="F13" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £38.50</t>
-      </text>
-    </comment>
-    <comment ref="F14" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £45.69</t>
-      </text>
-    </comment>
-    <comment ref="F15" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £46.95</t>
-      </text>
-    </comment>
-    <comment ref="F16" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £48.32</t>
-      </text>
-    </comment>
-    <comment ref="F17" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £784.70</t>
-      </text>
-    </comment>
-    <comment ref="L17" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £785.93</t>
-      </text>
-    </comment>
-    <comment ref="F18" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £1,005.07</t>
-      </text>
-    </comment>
-    <comment ref="F19" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £38.16</t>
-      </text>
-    </comment>
-    <comment ref="L19" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £31.88</t>
-      </text>
-    </comment>
-    <comment ref="F20" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £47.84</t>
-      </text>
-    </comment>
-    <comment ref="L20" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £38.70</t>
-      </text>
-    </comment>
-    <comment ref="F21" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £50.47</t>
-      </text>
-    </comment>
-    <comment ref="L21" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £40.25</t>
-      </text>
-    </comment>
-    <comment ref="F22" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £56.44</t>
-      </text>
-    </comment>
-    <comment ref="L22" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £46.95</t>
-      </text>
-    </comment>
-    <comment ref="F23" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £48.91</t>
-      </text>
-    </comment>
-    <comment ref="F24" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £47.25</t>
-      </text>
-    </comment>
-    <comment ref="F26" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £48.32</t>
-      </text>
-    </comment>
-    <comment ref="L26" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £47.08</t>
-      </text>
-    </comment>
-    <comment ref="F27" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £1,252.32</t>
-      </text>
-    </comment>
-    <comment ref="F28" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £1,370.57</t>
-      </text>
-    </comment>
-    <comment ref="F29" authorId="0" shapeId="0">
-      <text>
-        <t>Previous Price: £1,306.07</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -743,7 +558,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>£12.60</t>
+          <t>£11.40</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -840,7 +655,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>£14.46</t>
+          <t>£13.28</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -917,17 +732,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£17.15</t>
+          <t>£17.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£17.15</t>
+          <t>£17.00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£17.15</t>
+          <t>£17.00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -937,7 +752,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>£17.97</t>
+          <t>£16.83</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1014,17 +829,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>£17.50</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>£18.22</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>£18.22</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£18.22</t>
+          <t>£17.50</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1034,7 +849,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>£18.79</t>
+          <t>£17.93</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1111,17 +926,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£23.11</t>
+          <t>£22.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£23.11</t>
+          <t>£22.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£23.11</t>
+          <t>£22.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1131,7 +946,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>£24.26</t>
+          <t>£21.92</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1208,17 +1023,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£24.68</t>
+          <t>£24.60</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£24.68</t>
+          <t>£24.60</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£24.68</t>
+          <t>£24.60</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1228,7 +1043,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>£26.69</t>
+          <t>£23.64</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1305,17 +1120,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£25.00</t>
+          <t>£24.00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£25.00</t>
+          <t>£24.00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£25.00</t>
+          <t>£24.00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1325,7 +1140,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>£26.74</t>
+          <t>£24.17</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1402,17 +1217,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£28.97</t>
+          <t>£27.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£28.97</t>
+          <t>£27.00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£28.97</t>
+          <t>£27.00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1422,7 +1237,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>£30.33</t>
+          <t>£27.00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1499,17 +1314,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£31.95</t>
+          <t>£30.50</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£31.95</t>
+          <t>£30.50</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£31.95</t>
+          <t>£30.50</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1519,7 +1334,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>£33.37</t>
+          <t>£29.50</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1596,17 +1411,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£30.83</t>
+          <t>£29.50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£30.83</t>
+          <t>£29.50</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£30.83</t>
+          <t>£29.50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1616,7 +1431,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>£31.57</t>
+          <t>£30.42</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1693,52 +1508,52 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>£37.50</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>£37.50</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>£37.50</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>£37.50</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>£38.06</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>£40.65</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>£41.18</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>£41.79</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>£40.65</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>£40.65</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>£37.50</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>£42.12</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>£40.65</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>£41.18</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>£41.79</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>£40.65</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1753,7 +1568,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1790,17 +1605,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£37.57</t>
+          <t>£37.50</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£37.57</t>
+          <t>£37.50</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£37.57</t>
+          <t>£37.50</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1810,7 +1625,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>£40.31</t>
+          <t>£36.46</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1865,7 +1680,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1887,17 +1702,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£45.53</t>
+          <t>£44.00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£45.53</t>
+          <t>£44.00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£45.53</t>
+          <t>£44.00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1907,7 +1722,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>£48.06</t>
+          <t>£45.00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1984,39 +1799,39 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>£46.00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>£46.00</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>£46.00</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>£46.88</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>£46.80</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>£46.88</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>No Link</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>£46.00</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>£49.05</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>£46.80</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>£46.88</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>£47.29</t>
@@ -2064,7 +1879,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2101,7 +1916,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>£49.41</t>
+          <t>£45.68</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2178,17 +1993,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£768.00</t>
+          <t>£730.00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>£768.00</t>
+          <t>£730.00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>£768.00</t>
+          <t>£730.00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2218,7 +2033,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2228,7 +2043,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2238,7 +2053,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2248,7 +2063,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2258,7 +2073,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2275,17 +2090,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>£984.00</t>
+          <t>£940.00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>£984.00</t>
+          <t>£940.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>£984.00</t>
+          <t>£940.00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2335,7 +2150,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2345,7 +2160,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2539,12 +2354,12 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>£49.55</t>
+          <t>POA or OOS</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2663,17 +2478,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>£52.00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>£52.30</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>£52.30</t>
-        </is>
-      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>£52.30</t>
+          <t>£52.00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2733,7 +2548,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2760,34 +2575,34 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>£45.50</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>£45.50</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>£45.50</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>£45.50</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>£58.51</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>£48.91</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>£48.91</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>£48.91</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>£45.50</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>£51.80</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>£48.91</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>£58.00</t>
@@ -2800,7 +2615,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2857,34 +2672,34 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>£44.00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>£44.00</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>£44.00</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>£44.00</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>£53.49</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>£47.08</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>£47.08</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>£47.08</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>£44.00</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>£53.49</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>£47.08</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>£61.00</t>
@@ -2897,7 +2712,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2969,12 +2784,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2984,22 +2799,22 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3009,12 +2824,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3024,7 +2839,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -3034,7 +2849,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3051,34 +2866,34 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>£45.00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>£45.00</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>£45.00</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>£45.00</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>£55.89</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>£48.00</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>£48.00</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>£48.00</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>£45.00</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>£52.95</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>£48.00</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>£58.00</t>
@@ -3091,7 +2906,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3148,17 +2963,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>£1,250.23</t>
+          <t>£1,200.00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>£1,250.23</t>
+          <t>£1,200.00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>£1,250.23</t>
+          <t>£1,200.00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3168,7 +2983,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>£1311.36</t>
+          <t>£937.44</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3188,7 +3003,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3198,7 +3013,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3218,12 +3033,12 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3245,17 +3060,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>£1,363.10</t>
+          <t>£1,250.00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>£1,363.10</t>
+          <t>£1,250.00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>£1,363.10</t>
+          <t>£1,250.00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3285,7 +3100,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3295,7 +3110,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3315,12 +3130,12 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3342,17 +3157,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>£1,300.75</t>
+          <t>£1,225.00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>£1,300.75</t>
+          <t>£1,225.00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>£1,300.75</t>
+          <t>£1,225.00</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3372,7 +3187,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3382,7 +3197,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3392,7 +3207,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3402,7 +3217,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3412,12 +3227,12 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>No Link</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3428,6 +3243,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>